--- a/Pruebas calificadas/COLEGIO EMMA REYES (IED)_701_CALIFICADO.xlsx
+++ b/Pruebas calificadas/COLEGIO EMMA REYES (IED)_701_CALIFICADO.xlsx
@@ -11460,9 +11460,9 @@
           <t>D</t>
         </is>
       </c>
-      <c r="L44" s="6" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="L44" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
@@ -11962,9 +11962,9 @@
           <t>D</t>
         </is>
       </c>
-      <c r="L46" s="6" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="L46" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
@@ -12215,9 +12215,9 @@
           <t>D</t>
         </is>
       </c>
-      <c r="L47" s="6" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="L47" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
@@ -12468,9 +12468,9 @@
           <t>D</t>
         </is>
       </c>
-      <c r="L48" s="6" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="L48" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
@@ -12721,9 +12721,9 @@
           <t>D</t>
         </is>
       </c>
-      <c r="L49" s="6" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="L49" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
@@ -13223,9 +13223,9 @@
           <t>D</t>
         </is>
       </c>
-      <c r="L51" s="6" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="L51" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
@@ -13725,9 +13725,9 @@
           <t>D</t>
         </is>
       </c>
-      <c r="L53" s="6" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="L53" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
@@ -13978,9 +13978,9 @@
           <t>D</t>
         </is>
       </c>
-      <c r="L54" s="6" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="L54" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
@@ -14737,9 +14737,9 @@
           <t>D</t>
         </is>
       </c>
-      <c r="L57" s="6" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="L57" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
@@ -14990,9 +14990,9 @@
           <t>D</t>
         </is>
       </c>
-      <c r="L58" s="6" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="L58" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
@@ -15243,9 +15243,9 @@
           <t>D</t>
         </is>
       </c>
-      <c r="L59" s="6" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="L59" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
@@ -15496,9 +15496,9 @@
           <t>D</t>
         </is>
       </c>
-      <c r="L60" s="6" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="L60" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
@@ -15749,9 +15749,9 @@
           <t>D</t>
         </is>
       </c>
-      <c r="L61" s="6" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="L61" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
@@ -16002,9 +16002,9 @@
           <t>D</t>
         </is>
       </c>
-      <c r="L62" s="6" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="L62" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
@@ -16255,9 +16255,9 @@
           <t>D</t>
         </is>
       </c>
-      <c r="L63" s="6" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="L63" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
@@ -16508,9 +16508,9 @@
           <t>D</t>
         </is>
       </c>
-      <c r="L64" s="6" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="L64" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
@@ -17014,9 +17014,9 @@
           <t>D</t>
         </is>
       </c>
-      <c r="L66" s="6" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="L66" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
@@ -17267,9 +17267,9 @@
           <t>D</t>
         </is>
       </c>
-      <c r="L67" s="6" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="L67" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
@@ -17773,9 +17773,9 @@
           <t>D</t>
         </is>
       </c>
-      <c r="L69" s="6" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="L69" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
@@ -18026,9 +18026,9 @@
           <t>D</t>
         </is>
       </c>
-      <c r="L70" s="6" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="L70" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
@@ -18279,9 +18279,9 @@
           <t>D</t>
         </is>
       </c>
-      <c r="L71" s="6" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="L71" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
@@ -18532,9 +18532,9 @@
           <t>D</t>
         </is>
       </c>
-      <c r="L72" s="6" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="L72" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
@@ -18785,9 +18785,9 @@
           <t>D</t>
         </is>
       </c>
-      <c r="L73" s="6" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="L73" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
@@ -19038,9 +19038,9 @@
           <t>B</t>
         </is>
       </c>
-      <c r="L74" s="3" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+      <c r="L74" s="6" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
@@ -19291,9 +19291,9 @@
           <t>D</t>
         </is>
       </c>
-      <c r="L75" s="6" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="L75" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="M75" s="2" t="inlineStr">
@@ -19544,9 +19544,9 @@
           <t>D</t>
         </is>
       </c>
-      <c r="L76" s="6" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="L76" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="M76" s="2" t="inlineStr">
@@ -20299,9 +20299,9 @@
           <t>D</t>
         </is>
       </c>
-      <c r="L79" s="6" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="L79" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="M79" s="2" t="inlineStr">

--- a/Pruebas calificadas/COLEGIO EMMA REYES (IED)_701_CALIFICADO.xlsx
+++ b/Pruebas calificadas/COLEGIO EMMA REYES (IED)_701_CALIFICADO.xlsx
@@ -807,11 +807,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A2" s="2" t="inlineStr"/>
       <c r="B2" s="2" t="inlineStr">
         <is>
           <t>111001800554</t>
@@ -1060,11 +1056,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A3" s="2" t="inlineStr"/>
       <c r="B3" s="2" t="inlineStr">
         <is>
           <t>111001800554</t>
@@ -1313,11 +1305,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A4" s="2" t="inlineStr"/>
       <c r="B4" s="2" t="inlineStr">
         <is>
           <t>111001800554</t>
@@ -1566,11 +1554,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A5" s="2" t="inlineStr"/>
       <c r="B5" s="2" t="inlineStr">
         <is>
           <t>111001800554</t>
@@ -1819,11 +1803,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A6" s="2" t="inlineStr"/>
       <c r="B6" s="2" t="inlineStr">
         <is>
           <t>111001800554</t>
@@ -2072,11 +2052,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A7" s="2" t="inlineStr"/>
       <c r="B7" s="2" t="inlineStr">
         <is>
           <t>111001800554</t>
@@ -2325,11 +2301,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A8" s="2" t="inlineStr"/>
       <c r="B8" s="2" t="inlineStr">
         <is>
           <t>111001800554</t>
@@ -2578,11 +2550,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A9" s="2" t="inlineStr"/>
       <c r="B9" s="2" t="inlineStr">
         <is>
           <t>111001800554</t>
@@ -2831,11 +2799,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A10" s="2" t="inlineStr"/>
       <c r="B10" s="2" t="inlineStr">
         <is>
           <t>111001800554</t>
@@ -3084,11 +3048,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A11" s="2" t="inlineStr"/>
       <c r="B11" s="2" t="inlineStr">
         <is>
           <t>111001800554</t>
@@ -3337,11 +3297,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A12" s="2" t="inlineStr"/>
       <c r="B12" s="2" t="inlineStr">
         <is>
           <t>111001800554</t>
@@ -3590,11 +3546,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A13" s="2" t="inlineStr"/>
       <c r="B13" s="2" t="inlineStr">
         <is>
           <t>111001800554</t>
@@ -3843,11 +3795,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A14" s="2" t="inlineStr"/>
       <c r="B14" s="2" t="inlineStr">
         <is>
           <t>111001800554</t>
@@ -4096,11 +4044,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A15" s="2" t="inlineStr"/>
       <c r="B15" s="2" t="inlineStr">
         <is>
           <t>111001800554</t>
@@ -4349,11 +4293,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A16" s="2" t="inlineStr"/>
       <c r="B16" s="2" t="inlineStr">
         <is>
           <t>111001800554</t>
@@ -4602,11 +4542,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A17" s="2" t="inlineStr"/>
       <c r="B17" s="2" t="inlineStr">
         <is>
           <t>111001800554</t>
@@ -4855,11 +4791,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A18" s="2" t="inlineStr"/>
       <c r="B18" s="2" t="inlineStr">
         <is>
           <t>111001800554</t>
@@ -5108,11 +5040,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A19" s="2" t="inlineStr"/>
       <c r="B19" s="2" t="inlineStr">
         <is>
           <t>111001800554</t>
@@ -5357,11 +5285,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A20" s="2" t="inlineStr"/>
       <c r="B20" s="2" t="inlineStr">
         <is>
           <t>111001800554</t>
@@ -5610,11 +5534,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A21" s="2" t="inlineStr"/>
       <c r="B21" s="2" t="inlineStr">
         <is>
           <t>111001800554</t>
@@ -5863,11 +5783,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A22" s="2" t="inlineStr"/>
       <c r="B22" s="2" t="inlineStr">
         <is>
           <t>111001800554</t>
@@ -6116,11 +6032,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A23" s="2" t="inlineStr"/>
       <c r="B23" s="2" t="inlineStr">
         <is>
           <t>111001800554</t>
@@ -6369,11 +6281,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A24" s="2" t="inlineStr"/>
       <c r="B24" s="2" t="inlineStr">
         <is>
           <t>111001800554</t>
@@ -6622,11 +6530,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A25" s="2" t="inlineStr"/>
       <c r="B25" s="2" t="inlineStr">
         <is>
           <t>111001800554</t>
@@ -6875,11 +6779,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A26" s="2" t="inlineStr"/>
       <c r="B26" s="2" t="inlineStr">
         <is>
           <t>111001800554</t>
@@ -7128,11 +7028,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A27" s="2" t="inlineStr"/>
       <c r="B27" s="2" t="inlineStr">
         <is>
           <t>111001800554</t>
@@ -7381,11 +7277,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A28" s="2" t="inlineStr"/>
       <c r="B28" s="2" t="inlineStr">
         <is>
           <t>111001800554</t>
@@ -7630,11 +7522,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A29" s="2" t="inlineStr"/>
       <c r="B29" s="2" t="inlineStr">
         <is>
           <t>111001800554</t>
@@ -7883,11 +7771,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A30" s="2" t="inlineStr"/>
       <c r="B30" s="2" t="inlineStr">
         <is>
           <t>111001800554</t>
@@ -8132,11 +8016,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A31" s="2" t="inlineStr"/>
       <c r="B31" s="2" t="inlineStr">
         <is>
           <t>111001800554</t>
@@ -8385,11 +8265,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A32" s="2" t="inlineStr"/>
       <c r="B32" s="2" t="inlineStr">
         <is>
           <t>111001800554</t>
@@ -8634,11 +8510,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A33" s="2" t="inlineStr"/>
       <c r="B33" s="2" t="inlineStr">
         <is>
           <t>111001800554</t>
@@ -8887,11 +8759,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A34" s="2" t="inlineStr"/>
       <c r="B34" s="2" t="inlineStr">
         <is>
           <t>111001800554</t>
@@ -9140,11 +9008,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A35" s="2" t="inlineStr"/>
       <c r="B35" s="2" t="inlineStr">
         <is>
           <t>111001800554</t>
@@ -9393,11 +9257,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A36" s="2" t="inlineStr"/>
       <c r="B36" s="2" t="inlineStr">
         <is>
           <t>111001800554</t>
@@ -9638,11 +9498,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A37" s="2" t="inlineStr"/>
       <c r="B37" s="2" t="inlineStr">
         <is>
           <t>111001800554</t>
@@ -9891,11 +9747,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A38" s="2" t="inlineStr"/>
       <c r="B38" s="2" t="inlineStr">
         <is>
           <t>111001800554</t>
@@ -10144,11 +9996,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A39" s="2" t="inlineStr"/>
       <c r="B39" s="2" t="inlineStr">
         <is>
           <t>111001800554</t>
@@ -10397,11 +10245,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A40" s="2" t="inlineStr"/>
       <c r="B40" s="2" t="inlineStr">
         <is>
           <t>111001800554</t>
@@ -10650,11 +10494,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A41" s="2" t="inlineStr"/>
       <c r="B41" s="2" t="inlineStr">
         <is>
           <t>111001800554</t>
@@ -10903,11 +10743,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A42" s="2" t="inlineStr"/>
       <c r="B42" s="2" t="inlineStr">
         <is>
           <t>111001800554</t>
@@ -11156,11 +10992,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A43" s="2" t="inlineStr"/>
       <c r="B43" s="2" t="inlineStr">
         <is>
           <t>111001800554</t>
@@ -11409,11 +11241,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A44" s="2" t="inlineStr"/>
       <c r="B44" s="2" t="inlineStr">
         <is>
           <t>111001800554</t>
@@ -11662,11 +11490,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A45" s="2" t="inlineStr"/>
       <c r="B45" s="2" t="inlineStr">
         <is>
           <t>111001800554</t>
@@ -11911,11 +11735,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A46" s="2" t="inlineStr"/>
       <c r="B46" s="2" t="inlineStr">
         <is>
           <t>111001800554</t>
@@ -12164,11 +11984,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A47" s="2" t="inlineStr"/>
       <c r="B47" s="2" t="inlineStr">
         <is>
           <t>111001800554</t>
@@ -12417,11 +12233,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A48" s="2" t="inlineStr"/>
       <c r="B48" s="2" t="inlineStr">
         <is>
           <t>111001800554</t>
@@ -12670,11 +12482,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A49" s="2" t="inlineStr"/>
       <c r="B49" s="2" t="inlineStr">
         <is>
           <t>111001800554</t>
@@ -12923,11 +12731,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A50" s="2" t="inlineStr"/>
       <c r="B50" s="2" t="inlineStr">
         <is>
           <t>111001800554</t>
@@ -13172,11 +12976,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A51" s="2" t="inlineStr"/>
       <c r="B51" s="2" t="inlineStr">
         <is>
           <t>111001800554</t>
@@ -13421,11 +13221,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A52" s="2" t="inlineStr"/>
       <c r="B52" s="2" t="inlineStr">
         <is>
           <t>111001800554</t>
@@ -13674,11 +13470,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A53" s="2" t="inlineStr"/>
       <c r="B53" s="2" t="inlineStr">
         <is>
           <t>111001800554</t>
@@ -13927,11 +13719,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A54" s="2" t="inlineStr"/>
       <c r="B54" s="2" t="inlineStr">
         <is>
           <t>111001800554</t>
@@ -14180,11 +13968,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A55" s="2" t="inlineStr"/>
       <c r="B55" s="2" t="inlineStr">
         <is>
           <t>111001800554</t>
@@ -14433,11 +14217,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A56" s="2" t="inlineStr"/>
       <c r="B56" s="2" t="inlineStr">
         <is>
           <t>111001800554</t>
@@ -14686,11 +14466,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A57" s="2" t="inlineStr"/>
       <c r="B57" s="2" t="inlineStr">
         <is>
           <t>111001800554</t>
@@ -14939,11 +14715,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A58" s="2" t="inlineStr"/>
       <c r="B58" s="2" t="inlineStr">
         <is>
           <t>111001800554</t>
@@ -15192,11 +14964,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A59" s="2" t="inlineStr"/>
       <c r="B59" s="2" t="inlineStr">
         <is>
           <t>111001800554</t>
@@ -15445,11 +15213,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A60" s="2" t="inlineStr"/>
       <c r="B60" s="2" t="inlineStr">
         <is>
           <t>111001800554</t>
@@ -15698,11 +15462,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A61" s="2" t="inlineStr"/>
       <c r="B61" s="2" t="inlineStr">
         <is>
           <t>111001800554</t>
@@ -15951,11 +15711,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A62" s="2" t="inlineStr"/>
       <c r="B62" s="2" t="inlineStr">
         <is>
           <t>111001800554</t>
@@ -16204,11 +15960,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A63" s="2" t="inlineStr"/>
       <c r="B63" s="2" t="inlineStr">
         <is>
           <t>111001800554</t>
@@ -16457,11 +16209,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A64" s="2" t="inlineStr"/>
       <c r="B64" s="2" t="inlineStr">
         <is>
           <t>111001800554</t>
@@ -16710,11 +16458,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A65" s="2" t="inlineStr"/>
       <c r="B65" s="2" t="inlineStr">
         <is>
           <t>111001800554</t>
@@ -16963,11 +16707,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A66" s="2" t="inlineStr"/>
       <c r="B66" s="2" t="inlineStr">
         <is>
           <t>111001800554</t>
@@ -17216,11 +16956,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A67" s="2" t="inlineStr"/>
       <c r="B67" s="2" t="inlineStr">
         <is>
           <t>111001800554</t>
@@ -17469,11 +17205,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A68" s="2" t="inlineStr"/>
       <c r="B68" s="2" t="inlineStr">
         <is>
           <t>111001800554</t>
@@ -17722,11 +17454,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A69" s="2" t="inlineStr"/>
       <c r="B69" s="2" t="inlineStr">
         <is>
           <t>111001800554</t>
@@ -17975,11 +17703,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A70" s="2" t="inlineStr"/>
       <c r="B70" s="2" t="inlineStr">
         <is>
           <t>111001800554</t>
@@ -18228,11 +17952,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A71" s="2" t="inlineStr"/>
       <c r="B71" s="2" t="inlineStr">
         <is>
           <t>111001800554</t>
@@ -18481,11 +18201,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A72" s="2" t="inlineStr"/>
       <c r="B72" s="2" t="inlineStr">
         <is>
           <t>111001800554</t>
@@ -18734,11 +18450,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A73" s="2" t="inlineStr"/>
       <c r="B73" s="2" t="inlineStr">
         <is>
           <t>111001800554</t>
@@ -18987,11 +18699,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A74" s="2" t="inlineStr"/>
       <c r="B74" s="2" t="inlineStr">
         <is>
           <t>111001800554</t>
@@ -19240,11 +18948,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A75" s="2" t="inlineStr"/>
       <c r="B75" s="2" t="inlineStr">
         <is>
           <t>111001800554</t>
@@ -19493,11 +19197,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A76" s="2" t="inlineStr"/>
       <c r="B76" s="2" t="inlineStr">
         <is>
           <t>111001800554</t>
@@ -19746,11 +19446,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A77" s="2" t="inlineStr"/>
       <c r="B77" s="2" t="inlineStr">
         <is>
           <t>111001800554</t>
@@ -19999,11 +19695,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A78" s="2" t="inlineStr"/>
       <c r="B78" s="2" t="inlineStr">
         <is>
           <t>111001800554</t>
@@ -20248,11 +19940,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A79" s="2" t="inlineStr"/>
       <c r="B79" s="2" t="inlineStr">
         <is>
           <t>111001800554</t>
@@ -20501,11 +20189,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A80" s="2" t="inlineStr"/>
       <c r="B80" s="2" t="inlineStr">
         <is>
           <t>111001800554</t>
@@ -20754,11 +20438,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A81" s="2" t="inlineStr"/>
       <c r="B81" s="2" t="inlineStr">
         <is>
           <t>111001800554</t>
